--- a/Calibration/Book1.xlsx
+++ b/Calibration/Book1.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Github\Proa-II-Electrical-Setup\Calibration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6AFDF39-A86B-44DA-AD44-21B05E801077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85B24E68-F38F-4218-A717-E359A39D6F68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{D441ABFB-7FD8-48AA-B09E-E56FC10E3D76}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{D441ABFB-7FD8-48AA-B09E-E56FC10E3D76}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
   <si>
     <t>ADS1115 Reading</t>
   </si>
@@ -57,6 +58,21 @@
   </si>
   <si>
     <t>Column1</t>
+  </si>
+  <si>
+    <t>ADS Reading</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>Reading</t>
   </si>
 </sst>
 </file>
@@ -92,13 +108,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -495,6 +520,660 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ADS Reading</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-5.5723488683764644E-2"/>
+                  <c:y val="5.6752554673076966E-3"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet2!$A$2:$A$52</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="51"/>
+                <c:pt idx="0" formatCode="0.00">
+                  <c:v>55.2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>52.8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>52.4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>53.6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>53.9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>51.8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>51.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>53.1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>53.1</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>50.9</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>52.1</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>52.3</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>52.4</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>50.9</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>50.4</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>50.2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>51.4</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>51.7</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>51.8</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>49.8</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>49.6</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>51.2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>51.2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>51.3</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>49.5</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>50.7</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>50.8</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>50.2</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>48.1</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>49.4</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>49.4</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>47.6</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>49.1</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>45.1</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46.7</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>48.2</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>21.3</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>22.1</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>22.8</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>23.5</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>23.3</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>24.5</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>24.3</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>24.8</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>24.5</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>24.7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet2!$B$2:$B$52</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="51"/>
+                <c:pt idx="0" formatCode="0.00">
+                  <c:v>24273</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>23145</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>22989</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>23524</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>23690</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>23710</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>23738</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>22720</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>22609</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>23276</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>23302</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>23311</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>22354</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>22817</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>22974</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>22988</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>22329</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>22107</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>22031</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>22581</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>22695</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22729</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>21821</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>21779</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>22446</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>22500</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>22519</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>21714</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>22258</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>22293</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>21945</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>22034</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>21102</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>21686</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>21697</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>20892</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>21545</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>19864</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>20495</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>21172</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>9291</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>9699</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>10005</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>10301</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>10240</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>10547</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>10773</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>10683</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>10866</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>10775</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>10852</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-262D-43F7-8DAC-42BFACDE10ED}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1072997632"/>
+        <c:axId val="1072990432"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1072997632"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1072990432"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1072990432"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1072997632"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -535,7 +1214,563 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -1092,6 +2327,47 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>600324</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>71396</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>607944</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>75205</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF564556-9860-8BA0-04E0-49BA2AA3ADE2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BD8666AF-50BB-4BBE-9FD2-6D56DEE8FA0B}" name="Table1" displayName="Table1" ref="A2:F10" totalsRowShown="0">
   <autoFilter ref="A2:F10" xr:uid="{BD8666AF-50BB-4BBE-9FD2-6D56DEE8FA0B}"/>
@@ -1106,6 +2382,17 @@
     <tableColumn id="6" xr3:uid="{A415919F-2849-4A91-8788-9EC076FAC791}" name="Column1">
       <calculatedColumnFormula>C3/D3</calculatedColumnFormula>
     </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0D1353D7-DDA0-49DE-8ED9-2AF68BFC090F}" name="Table3" displayName="Table3" ref="A1:B52" totalsRowShown="0">
+  <autoFilter ref="A1:B52" xr:uid="{0D1353D7-DDA0-49DE-8ED9-2AF68BFC090F}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{50135BE6-A35C-4F74-8EBD-08A89CE7B679}" name="Voltage" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{CBD67CD9-5644-4CF7-ABBB-1F343E99C38D}" name="ADS Reading" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1647,4 +2934,907 @@
     <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{841DC4AD-CB62-4AC7-86A3-A9EEBC7FEAA5}">
+  <dimension ref="A1:I62"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.109375" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>55.2</v>
+      </c>
+      <c r="B2" s="2">
+        <v>24273</v>
+      </c>
+      <c r="E2">
+        <v>439.01</v>
+      </c>
+      <c r="F2">
+        <v>-2.4315000000000002</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <f>H2*$E$2+$F$2</f>
+        <v>-2.4315000000000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>52.8</v>
+      </c>
+      <c r="B3" s="1">
+        <v>23145</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <f t="shared" ref="I3:I62" si="0">H3*$E$2+$F$2</f>
+        <v>436.57849999999996</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>52.4</v>
+      </c>
+      <c r="B4" s="1">
+        <v>22989</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="0"/>
+        <v>875.58849999999995</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>53.6</v>
+      </c>
+      <c r="B5" s="1">
+        <v>23524</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="0"/>
+        <v>1314.5985000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>53.9</v>
+      </c>
+      <c r="B6" s="1">
+        <v>23690</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="0"/>
+        <v>1753.6085</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>54</v>
+      </c>
+      <c r="B7" s="1">
+        <v>23710</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="0"/>
+        <v>2192.6185</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>54</v>
+      </c>
+      <c r="B8" s="1">
+        <v>23738</v>
+      </c>
+      <c r="H8">
+        <v>6</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="0"/>
+        <v>2631.6284999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>51.8</v>
+      </c>
+      <c r="B9" s="1">
+        <v>22720</v>
+      </c>
+      <c r="H9">
+        <v>7</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="0"/>
+        <v>3070.6384999999996</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>51.5</v>
+      </c>
+      <c r="B10" s="1">
+        <v>22609</v>
+      </c>
+      <c r="H10">
+        <v>8</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="0"/>
+        <v>3509.6484999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>53</v>
+      </c>
+      <c r="B11" s="1">
+        <v>23276</v>
+      </c>
+      <c r="H11">
+        <v>9</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="0"/>
+        <v>3948.6585</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>53.1</v>
+      </c>
+      <c r="B12" s="1">
+        <v>23302</v>
+      </c>
+      <c r="H12">
+        <v>10</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="0"/>
+        <v>4387.6685000000007</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>53.1</v>
+      </c>
+      <c r="B13" s="1">
+        <v>23311</v>
+      </c>
+      <c r="H13">
+        <v>11</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="0"/>
+        <v>4826.6785</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>50.9</v>
+      </c>
+      <c r="B14" s="1">
+        <v>22354</v>
+      </c>
+      <c r="H14">
+        <v>12</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="0"/>
+        <v>5265.6885000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>52.1</v>
+      </c>
+      <c r="B15" s="1">
+        <v>22817</v>
+      </c>
+      <c r="H15">
+        <v>13</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="0"/>
+        <v>5704.6985000000004</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>52.3</v>
+      </c>
+      <c r="B16" s="1">
+        <v>22974</v>
+      </c>
+      <c r="H16">
+        <v>14</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="0"/>
+        <v>6143.7084999999997</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>52.4</v>
+      </c>
+      <c r="B17" s="1">
+        <v>22988</v>
+      </c>
+      <c r="H17">
+        <v>15</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="0"/>
+        <v>6582.7184999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>50.9</v>
+      </c>
+      <c r="B18" s="1">
+        <v>22329</v>
+      </c>
+      <c r="H18">
+        <v>16</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="0"/>
+        <v>7021.7285000000002</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>50.4</v>
+      </c>
+      <c r="B19" s="1">
+        <v>22107</v>
+      </c>
+      <c r="H19">
+        <v>17</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="0"/>
+        <v>7460.7385000000004</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>50.2</v>
+      </c>
+      <c r="B20" s="1">
+        <v>22031</v>
+      </c>
+      <c r="H20">
+        <v>18</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="0"/>
+        <v>7899.7485000000006</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>51.4</v>
+      </c>
+      <c r="B21" s="1">
+        <v>22581</v>
+      </c>
+      <c r="H21">
+        <v>19</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="0"/>
+        <v>8338.7584999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>51.7</v>
+      </c>
+      <c r="B22" s="1">
+        <v>22695</v>
+      </c>
+      <c r="H22">
+        <v>20</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="0"/>
+        <v>8777.7685000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>51.8</v>
+      </c>
+      <c r="B23" s="1">
+        <v>22729</v>
+      </c>
+      <c r="H23">
+        <v>21</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="0"/>
+        <v>9216.7784999999985</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>49.8</v>
+      </c>
+      <c r="B24" s="1">
+        <v>21821</v>
+      </c>
+      <c r="H24">
+        <v>22</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="0"/>
+        <v>9655.7884999999987</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>49.6</v>
+      </c>
+      <c r="B25" s="1">
+        <v>21779</v>
+      </c>
+      <c r="H25">
+        <v>23</v>
+      </c>
+      <c r="I25">
+        <f t="shared" si="0"/>
+        <v>10094.798499999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>51.2</v>
+      </c>
+      <c r="B26" s="1">
+        <v>22446</v>
+      </c>
+      <c r="H26">
+        <v>24</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="0"/>
+        <v>10533.808499999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>51.2</v>
+      </c>
+      <c r="B27" s="1">
+        <v>22500</v>
+      </c>
+      <c r="H27">
+        <v>25</v>
+      </c>
+      <c r="I27">
+        <f t="shared" si="0"/>
+        <v>10972.818499999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>51.3</v>
+      </c>
+      <c r="B28" s="1">
+        <v>22519</v>
+      </c>
+      <c r="H28">
+        <v>26</v>
+      </c>
+      <c r="I28">
+        <f t="shared" si="0"/>
+        <v>11411.8285</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>49.5</v>
+      </c>
+      <c r="B29" s="1">
+        <v>21714</v>
+      </c>
+      <c r="H29">
+        <v>27</v>
+      </c>
+      <c r="I29">
+        <f t="shared" si="0"/>
+        <v>11850.8385</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>50.7</v>
+      </c>
+      <c r="B30" s="1">
+        <v>22258</v>
+      </c>
+      <c r="H30">
+        <v>28</v>
+      </c>
+      <c r="I30">
+        <f t="shared" si="0"/>
+        <v>12289.848499999998</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>50.8</v>
+      </c>
+      <c r="B31" s="1">
+        <v>22293</v>
+      </c>
+      <c r="H31">
+        <v>29</v>
+      </c>
+      <c r="I31">
+        <f t="shared" si="0"/>
+        <v>12728.858499999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>50</v>
+      </c>
+      <c r="B32" s="1">
+        <v>21945</v>
+      </c>
+      <c r="H32">
+        <v>30</v>
+      </c>
+      <c r="I32">
+        <f t="shared" si="0"/>
+        <v>13167.868499999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>50.2</v>
+      </c>
+      <c r="B33" s="1">
+        <v>22034</v>
+      </c>
+      <c r="H33">
+        <v>31</v>
+      </c>
+      <c r="I33">
+        <f t="shared" si="0"/>
+        <v>13606.878499999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>48.1</v>
+      </c>
+      <c r="B34" s="1">
+        <v>21102</v>
+      </c>
+      <c r="H34">
+        <v>32</v>
+      </c>
+      <c r="I34">
+        <f t="shared" si="0"/>
+        <v>14045.888499999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>49.4</v>
+      </c>
+      <c r="B35" s="1">
+        <v>21686</v>
+      </c>
+      <c r="H35">
+        <v>33</v>
+      </c>
+      <c r="I35">
+        <f t="shared" si="0"/>
+        <v>14484.898499999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <v>49.4</v>
+      </c>
+      <c r="B36" s="1">
+        <v>21697</v>
+      </c>
+      <c r="H36">
+        <v>34</v>
+      </c>
+      <c r="I36">
+        <f t="shared" si="0"/>
+        <v>14923.9085</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>47.6</v>
+      </c>
+      <c r="B37" s="1">
+        <v>20892</v>
+      </c>
+      <c r="H37">
+        <v>35</v>
+      </c>
+      <c r="I37">
+        <f t="shared" si="0"/>
+        <v>15362.9185</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>49.1</v>
+      </c>
+      <c r="B38" s="1">
+        <v>21545</v>
+      </c>
+      <c r="H38">
+        <v>36</v>
+      </c>
+      <c r="I38">
+        <f t="shared" si="0"/>
+        <v>15801.9285</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>45.1</v>
+      </c>
+      <c r="B39" s="1">
+        <v>19864</v>
+      </c>
+      <c r="H39">
+        <v>37</v>
+      </c>
+      <c r="I39">
+        <f t="shared" si="0"/>
+        <v>16240.938499999998</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>46.7</v>
+      </c>
+      <c r="B40" s="1">
+        <v>20495</v>
+      </c>
+      <c r="H40">
+        <v>38</v>
+      </c>
+      <c r="I40">
+        <f t="shared" si="0"/>
+        <v>16679.948500000002</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>48.2</v>
+      </c>
+      <c r="B41" s="1">
+        <v>21172</v>
+      </c>
+      <c r="H41">
+        <v>39</v>
+      </c>
+      <c r="I41">
+        <f t="shared" si="0"/>
+        <v>17118.958500000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>21.3</v>
+      </c>
+      <c r="B42" s="1">
+        <v>9291</v>
+      </c>
+      <c r="H42">
+        <v>40</v>
+      </c>
+      <c r="I42">
+        <f t="shared" si="0"/>
+        <v>17557.968500000003</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>22.1</v>
+      </c>
+      <c r="B43" s="1">
+        <v>9699</v>
+      </c>
+      <c r="H43">
+        <v>41</v>
+      </c>
+      <c r="I43">
+        <f t="shared" si="0"/>
+        <v>17996.978500000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <v>22.8</v>
+      </c>
+      <c r="B44" s="1">
+        <v>10005</v>
+      </c>
+      <c r="H44">
+        <v>42</v>
+      </c>
+      <c r="I44">
+        <f t="shared" si="0"/>
+        <v>18435.988499999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>23.5</v>
+      </c>
+      <c r="B45" s="1">
+        <v>10301</v>
+      </c>
+      <c r="H45">
+        <v>43</v>
+      </c>
+      <c r="I45">
+        <f t="shared" si="0"/>
+        <v>18874.998500000002</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
+        <v>23.3</v>
+      </c>
+      <c r="B46" s="1">
+        <v>10240</v>
+      </c>
+      <c r="H46">
+        <v>44</v>
+      </c>
+      <c r="I46">
+        <f t="shared" si="0"/>
+        <v>19314.0085</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
+        <v>24</v>
+      </c>
+      <c r="B47" s="1">
+        <v>10547</v>
+      </c>
+      <c r="H47">
+        <v>45</v>
+      </c>
+      <c r="I47">
+        <f t="shared" si="0"/>
+        <v>19753.018500000002</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
+        <v>24.5</v>
+      </c>
+      <c r="B48" s="1">
+        <v>10773</v>
+      </c>
+      <c r="H48">
+        <v>46</v>
+      </c>
+      <c r="I48">
+        <f t="shared" si="0"/>
+        <v>20192.0285</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
+        <v>24.3</v>
+      </c>
+      <c r="B49" s="1">
+        <v>10683</v>
+      </c>
+      <c r="H49">
+        <v>47</v>
+      </c>
+      <c r="I49">
+        <f t="shared" si="0"/>
+        <v>20631.038500000002</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A50" s="1">
+        <v>24.8</v>
+      </c>
+      <c r="B50" s="1">
+        <v>10866</v>
+      </c>
+      <c r="H50">
+        <v>48</v>
+      </c>
+      <c r="I50">
+        <f t="shared" si="0"/>
+        <v>21070.048500000001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A51" s="1">
+        <v>24.5</v>
+      </c>
+      <c r="B51" s="1">
+        <v>10775</v>
+      </c>
+      <c r="H51">
+        <v>49</v>
+      </c>
+      <c r="I51">
+        <f t="shared" si="0"/>
+        <v>21509.058499999999</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
+        <v>24.7</v>
+      </c>
+      <c r="B52" s="1">
+        <v>10852</v>
+      </c>
+      <c r="H52">
+        <v>50</v>
+      </c>
+      <c r="I52">
+        <f t="shared" si="0"/>
+        <v>21948.068500000001</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H53">
+        <v>51</v>
+      </c>
+      <c r="I53">
+        <f t="shared" si="0"/>
+        <v>22387.0785</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H54">
+        <v>52</v>
+      </c>
+      <c r="I54">
+        <f t="shared" si="0"/>
+        <v>22826.088500000002</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H55">
+        <v>53</v>
+      </c>
+      <c r="I55">
+        <f t="shared" si="0"/>
+        <v>23265.0985</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H56">
+        <v>54</v>
+      </c>
+      <c r="I56">
+        <f t="shared" si="0"/>
+        <v>23704.108500000002</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H57">
+        <v>55</v>
+      </c>
+      <c r="I57">
+        <f t="shared" si="0"/>
+        <v>24143.1185</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H58">
+        <v>56</v>
+      </c>
+      <c r="I58">
+        <f t="shared" si="0"/>
+        <v>24582.128499999999</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H59">
+        <v>57</v>
+      </c>
+      <c r="I59">
+        <f t="shared" si="0"/>
+        <v>25021.138500000001</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H60">
+        <v>58</v>
+      </c>
+      <c r="I60">
+        <f t="shared" si="0"/>
+        <v>25460.148499999999</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H61">
+        <v>59</v>
+      </c>
+      <c r="I61">
+        <f t="shared" si="0"/>
+        <v>25899.158500000001</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H62">
+        <v>60</v>
+      </c>
+      <c r="I62">
+        <f t="shared" si="0"/>
+        <v>26338.1685</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <tableParts count="1">
+    <tablePart r:id="rId3"/>
+  </tableParts>
+</worksheet>
 </file>